--- a/ABCL.xlsx
+++ b/ABCL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F6B79C-1BF2-4A86-B119-9D1E2B83F09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9EFD29-9D7A-49DC-8B9F-1BF0F89D0DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43275" yWindow="345" windowWidth="42840" windowHeight="19110" xr2:uid="{FE36D645-8410-4180-9CAC-35B704723A88}"/>
+    <workbookView xWindow="8980" yWindow="4440" windowWidth="21060" windowHeight="13820" xr2:uid="{FE36D645-8410-4180-9CAC-35B704723A88}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>Price</t>
   </si>
@@ -251,7 +251,22 @@
     <t>Phase</t>
   </si>
   <si>
-    <t>Filing</t>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Filing???</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>Vasomotor symptoms</t>
+  </si>
+  <si>
+    <t>NK3R</t>
+  </si>
+  <si>
+    <t>100%?</t>
   </si>
 </sst>
 </file>
@@ -387,7 +402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -413,6 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -731,16 +747,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A77B118-86A5-4BB4-B0F5-DF5AB0939AE2}">
   <dimension ref="B2:M17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="6.1796875" customWidth="1"/>
     <col min="13" max="13" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
@@ -762,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="12"/>
       <c r="C3" t="s">
         <v>12</v>
@@ -781,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>294.66553199999998</v>
+        <v>306.61146600000001</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="12"/>
       <c r="C4" t="s">
         <v>13</v>
@@ -804,11 +821,11 @@
       </c>
       <c r="L4" s="3">
         <f>+L2*L3</f>
-        <v>825.06348959999991</v>
+        <v>3038.5196280600003</v>
       </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -822,19 +839,28 @@
         <v>3</v>
       </c>
       <c r="L5" s="3">
-        <f>760.585+25+65.938</f>
-        <v>851.52300000000002</v>
+        <f>128.513+405.313</f>
+        <v>533.82600000000002</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>50</v>
       </c>
+      <c r="D6" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H6" s="13"/>
       <c r="K6" t="s">
@@ -844,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>51</v>
       </c>
@@ -858,7 +884,7 @@
         <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="13"/>
       <c r="K7" t="s">
@@ -866,31 +892,31 @@
       </c>
       <c r="L7" s="3">
         <f>+L4-L5+L6</f>
-        <v>-26.459510400000113</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+        <v>2504.6936280600003</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="F8" t="s">
         <v>45</v>
       </c>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="12"/>
       <c r="F9" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="12"/>
       <c r="F10" t="s">
         <v>48</v>
       </c>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>52</v>
       </c>
@@ -902,42 +928,42 @@
       </c>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="12"/>
       <c r="F12" t="s">
         <v>53</v>
       </c>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="12"/>
       <c r="F13" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="12"/>
       <c r="E14" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="12"/>
       <c r="E15" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="12"/>
       <c r="E16" t="s">
         <v>62</v>
       </c>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="14"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -956,19 +982,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4240F2CB-B771-4FC8-9F4E-8864AF060D69}">
   <dimension ref="A1:V23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="2"/>
+    <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
@@ -1030,7 +1056,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>43</v>
       </c>
@@ -1041,7 +1067,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>44</v>
       </c>
@@ -1052,7 +1078,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>41</v>
       </c>
@@ -1063,7 +1089,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>42</v>
       </c>
@@ -1095,7 +1121,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
@@ -1116,7 +1142,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
@@ -1139,7 +1165,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1162,7 +1188,7 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
@@ -1183,7 +1209,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1206,7 +1232,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1227,7 +1253,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>33</v>
       </c>
@@ -1248,7 +1274,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>34</v>
       </c>
@@ -1269,7 +1295,7 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
@@ -1292,7 +1318,7 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
@@ -1315,7 +1341,7 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
@@ -1336,7 +1362,7 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
@@ -1359,7 +1385,7 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
     </row>
-    <row r="20" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
@@ -1380,7 +1406,7 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
@@ -1403,7 +1429,7 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1416,7 +1442,7 @@
         <v>0.53733118082383546</v>
       </c>
     </row>
-    <row r="23" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>1</v>
       </c>
